--- a/DataDrivenProject/src/test/resources/data.xlsx
+++ b/DataDrivenProject/src/test/resources/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Expleo\DataDrivenProject\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA573811-7E6B-4C8C-904F-4E06D62C8498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E953E43A-2FCA-44F1-A2BC-048F3D9EEEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="3744" windowWidth="17280" windowHeight="8880" xr2:uid="{27ED6C39-31B7-448E-9E5B-0985767522E9}"/>
+    <workbookView xWindow="1740" yWindow="5304" windowWidth="17280" windowHeight="8880" xr2:uid="{27ED6C39-31B7-448E-9E5B-0985767522E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,9 @@
     <t>password</t>
   </si>
   <si>
-    <t>asda</t>
-  </si>
-  <si>
     <t>aadd</t>
   </si>
   <si>
-    <t>Danny</t>
-  </si>
-  <si>
     <t>1asdad</t>
   </si>
   <si>
@@ -58,6 +52,12 @@
   </si>
   <si>
     <t>jeyakaraj@gmail.com</t>
+  </si>
+  <si>
+    <t>Jasper</t>
+  </si>
+  <si>
+    <t>Robert</t>
   </si>
 </sst>
 </file>
@@ -425,7 +425,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -433,26 +433,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
